--- a/tables/consensus_genes.xlsx
+++ b/tables/consensus_genes.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">Gene</t>
   </si>
@@ -23,16 +23,13 @@
     <t xml:space="preserve">ACE</t>
   </si>
   <si>
+    <t xml:space="preserve">JAK1</t>
+  </si>
+  <si>
     <t xml:space="preserve">ABCG2</t>
   </si>
   <si>
-    <t xml:space="preserve">CASP1</t>
-  </si>
-  <si>
     <t xml:space="preserve">FGF1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANPEP</t>
   </si>
   <si>
     <t xml:space="preserve">EDNRB</t>
@@ -399,11 +396,6 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
